--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0db97a9e776b41ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2589272f6d3945e4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R16f41542a0f148f0"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R04ff68c6774a413b"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39fda868cae44f1c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4520be3b19ba4c80"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2589272f6d3945e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra2672d6df51b43cb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R04ff68c6774a413b"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R9b55b54d5bac4ab9"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4520be3b19ba4c80"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R769b056ae79c4070"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra2672d6df51b43cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5d7128e1ee034103"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R9b55b54d5bac4ab9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R014f93b48b904f45"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R769b056ae79c4070"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra160ad2ca8374fa1"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5d7128e1ee034103"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raee10343612f4b4b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R014f93b48b904f45"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R0b472c36ffe642d3"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra160ad2ca8374fa1"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c83a93ff7b346e2"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raee10343612f4b4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8ec85d90a7fe4947"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R0b472c36ffe642d3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R75241418180a41ab"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c83a93ff7b346e2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re91a3f5bfcb14b3b"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8ec85d90a7fe4947"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6acf200d59e84250"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R75241418180a41ab"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R52104b15d18b4261"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re91a3f5bfcb14b3b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R912272f75a22472b"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6acf200d59e84250"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb997307762a84069"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R52104b15d18b4261"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Re715746efc9447fa"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R912272f75a22472b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb83d82a45e194a71"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb997307762a84069"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra223704bc38349e4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Re715746efc9447fa"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R2b5ade0818ad40b7"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb83d82a45e194a71"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R334bdc8aacb54c79"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra223704bc38349e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdc56fa7c15b14012"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R2b5ade0818ad40b7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rf7ce487166f34a81"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R334bdc8aacb54c79"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ac5c7f961cc4908"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdc56fa7c15b14012"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb9b3aac958434920"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rf7ce487166f34a81"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R89d20a967b02409c"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ac5c7f961cc4908"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd92b039389a4435a"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb9b3aac958434920"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R584a91e687e649e7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R89d20a967b02409c"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Re8beda359c754e01"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd92b039389a4435a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd65625001f04bfc"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R584a91e687e649e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb84cd6f3141e4c31"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Re8beda359c754e01"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R045dc537efc64db8"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd65625001f04bfc"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ab70e329a4d4374"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb84cd6f3141e4c31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf446cabbd97d4b6b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R045dc537efc64db8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R044dd7a595cb495f"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ab70e329a4d4374"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e5db4bc29064315"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf446cabbd97d4b6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R01a36f10b05846f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R044dd7a595cb495f"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R069b3de4e5314377"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e5db4bc29064315"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb69713a4fe39446a"/>
 </x:worksheet>
 </file>